--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACC1670-F921-4ED3-B46D-49D5C1EE49A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7DE37C-BD8D-42FD-BAC6-01BF4F7E6A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="1110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1111">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3358,6 +3358,9 @@
   </si>
   <si>
     <t>SERVO ECO TRACTOR OIL-7.5 L</t>
+  </si>
+  <si>
+    <t>SERVO GEAR HP 90-20X1/2L-HDPE</t>
   </si>
 </sst>
 </file>
@@ -16011,8 +16014,15 @@
       </c>
     </row>
     <row r="1118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1118"/>
-      <c r="B1118"/>
+      <c r="A1118" s="1">
+        <v>2502175</v>
+      </c>
+      <c r="B1118" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C1118" s="1">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7DE37C-BD8D-42FD-BAC6-01BF4F7E6A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74C4849-D157-40AA-AEED-49966FAF715E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="1111">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3718,7 +3718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1118"/>
+  <dimension ref="A1:C1119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -16024,6 +16024,17 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1119" s="1">
+        <v>7442401</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>938</v>
+      </c>
+      <c r="C1119" s="1">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74C4849-D157-40AA-AEED-49966FAF715E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADD77A0-B4D7-4ED8-91C7-96291873E1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="1114">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3361,6 +3361,15 @@
   </si>
   <si>
     <t>SERVO GEAR HP 90-20X1/2L-HDPE</t>
+  </si>
+  <si>
+    <t>SERVO HYPERTORQ 15W-40-7.5 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO HYPERSPORT F5 10W-50-20 X1 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO HYPERTORQ 15W-40-15 L PROMO</t>
   </si>
 </sst>
 </file>
@@ -3718,10 +3727,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1119"/>
+  <dimension ref="A1:C1122"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" style="1"/>
   </cols>
@@ -16035,6 +16044,39 @@
         <v>210</v>
       </c>
     </row>
+    <row r="1120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1120" s="1">
+        <v>1340253</v>
+      </c>
+      <c r="B1120" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C1120" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1121" s="1">
+        <v>671340250</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C1121" s="1">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1122" s="1">
+        <v>622250229</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C1122" s="1">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADD77A0-B4D7-4ED8-91C7-96291873E1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9D2CB2-8DEA-470A-87BB-A579DE6BA322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="1118">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3370,6 +3370,18 @@
   </si>
   <si>
     <t>SERVO HYPERTORQ 15W-40-15 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO FLEET 15W-40-20 X 1 L</t>
+  </si>
+  <si>
+    <t>SERVO FLEET 20W-40-20 X 1 L</t>
+  </si>
+  <si>
+    <t>SERVO PRIDE 20W-40-20 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO FLEET 15W-40-20 L</t>
   </si>
 </sst>
 </file>
@@ -3727,7 +3739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1122"/>
+  <dimension ref="A1:C1126"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -16077,6 +16089,50 @@
         <v>20</v>
       </c>
     </row>
+    <row r="1123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1123">
+        <v>273640184</v>
+      </c>
+      <c r="B1123" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C1123" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1124">
+        <v>274850184</v>
+      </c>
+      <c r="B1124" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C1124" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1125">
+        <v>475920269</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C1125" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1126">
+        <v>273640265</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C1126" s="1">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9D2CB2-8DEA-470A-87BB-A579DE6BA322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC42F77D-57B6-4267-BDEB-944B12730142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="1118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="1119">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3382,6 +3382,9 @@
   </si>
   <si>
     <t>SERVO FLEET 15W-40-20 L</t>
+  </si>
+  <si>
+    <t>SERVO HYPERDRIVE 0W-16-210 L</t>
   </si>
 </sst>
 </file>
@@ -3739,7 +3742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1126"/>
+  <dimension ref="A1:C1127"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -16133,6 +16136,17 @@
         <v>20</v>
       </c>
     </row>
+    <row r="1127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1127" s="1">
+        <v>652010401</v>
+      </c>
+      <c r="B1127" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C1127" s="1">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC42F77D-57B6-4267-BDEB-944B12730142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F03BB83-5170-41C0-8DC7-F1CE51BEA603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="1120">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3385,6 +3385,9 @@
   </si>
   <si>
     <t>SERVO HYPERDRIVE 0W-16-210 L</t>
+  </si>
+  <si>
+    <t>SERVO PRIDE 20W-40-20 X 1 L</t>
   </si>
 </sst>
 </file>
@@ -3742,7 +3745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1127"/>
+  <dimension ref="A1:C1128"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -16147,6 +16150,17 @@
         <v>210</v>
       </c>
     </row>
+    <row r="1128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1128" s="1">
+        <v>475920184</v>
+      </c>
+      <c r="B1128" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C1128" s="1">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F03BB83-5170-41C0-8DC7-F1CE51BEA603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CB78A3-8262-4CF1-88DF-522EA28AF7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="1122">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3388,6 +3388,12 @@
   </si>
   <si>
     <t>SERVO PRIDE 20W-40-20 X 1 L</t>
+  </si>
+  <si>
+    <t>SERVO FLEET 15W-40-10 L</t>
+  </si>
+  <si>
+    <t>SERVO ZOOM 2T SUPREME-20 X 1 L</t>
   </si>
 </sst>
 </file>
@@ -3745,7 +3751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1128"/>
+  <dimension ref="A1:C1130"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -16161,6 +16167,28 @@
         <v>20</v>
       </c>
     </row>
+    <row r="1129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1129">
+        <v>273640242</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C1129" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1130" s="1">
+        <v>429000184</v>
+      </c>
+      <c r="B1130" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C1130" s="1">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CB78A3-8262-4CF1-88DF-522EA28AF7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC1F115-3B5A-4139-9493-31DFB62B1AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="1123">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3394,6 +3394,9 @@
   </si>
   <si>
     <t>SERVO ZOOM 2T SUPREME-20 X 1 L</t>
+  </si>
+  <si>
+    <t>SERVO HYPERDRIVE 5W-30-4X3.5 L PROMO</t>
   </si>
 </sst>
 </file>
@@ -3429,13 +3432,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3751,7 +3757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1130"/>
+  <dimension ref="A1:C1131"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -16189,6 +16195,17 @@
         <v>20</v>
       </c>
     </row>
+    <row r="1131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1131" s="3">
+        <v>651130111</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C1131" s="1">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
